--- a/backend/data/uploads/MES/2026-07-12_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-12_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D26D2CDC-C54F-4F24-9875-0E9046822AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{247514B2-8307-4261-B138-31707C217CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{724C5D94-FB7F-45A6-9987-4840F8F766E1}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{30233BBA-816B-4D9C-96A9-22FBCF1F40E2}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A157244-9BBD-4256-9297-5B8A7196178F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776D1583-D4B6-4422-867B-38F74BAD2696}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-12_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-12_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{247514B2-8307-4261-B138-31707C217CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C34CFBA-A1E4-40A6-B992-5EEFBB4EFEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{30233BBA-816B-4D9C-96A9-22FBCF1F40E2}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5F0897CA-6155-4C6B-BDAD-59CBA43B714A}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776D1583-D4B6-4422-867B-38F74BAD2696}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E85E8-9D9F-48D5-9DC5-1E029A56630B}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-12_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-12_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C34CFBA-A1E4-40A6-B992-5EEFBB4EFEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0483117C-394A-4B2E-870D-F92D8467B7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5F0897CA-6155-4C6B-BDAD-59CBA43B714A}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{CB03E15C-8AE9-420A-9634-F340BD3EF236}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E85E8-9D9F-48D5-9DC5-1E029A56630B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D63CB5-33D0-4E71-A186-BECDC67AAB03}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
